--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N81_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N81_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.78302091079197</v>
+        <v>3.539740898003695</v>
       </c>
       <c r="D2" t="n">
-        <v>55.19600548910655</v>
+        <v>8.969350891979815</v>
       </c>
       <c r="E2" t="n">
-        <v>15.42221723983943</v>
+        <v>2.506110301473907</v>
       </c>
       <c r="F2" t="n">
-        <v>14.62298148309293</v>
+        <v>2.376234491002601</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.88085682254194</v>
+        <v>7.130639233663065</v>
       </c>
       <c r="D3" t="n">
-        <v>42.87212779561038</v>
+        <v>6.966720766786687</v>
       </c>
       <c r="E3" t="n">
-        <v>15.42221723983943</v>
+        <v>2.506110301473907</v>
       </c>
       <c r="F3" t="n">
-        <v>14.62298148309293</v>
+        <v>2.376234491002601</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.22236189690026</v>
+        <v>8.973633808246293</v>
       </c>
       <c r="D4" t="n">
-        <v>52.6166922122363</v>
+        <v>8.5502124844884</v>
       </c>
       <c r="E4" t="n">
-        <v>15.42221723983943</v>
+        <v>2.506110301473907</v>
       </c>
       <c r="F4" t="n">
-        <v>14.62298148309293</v>
+        <v>2.376234491002601</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.71702052916327</v>
+        <v>8.566515835989032</v>
       </c>
       <c r="D5" t="n">
-        <v>50.5069115818719</v>
+        <v>8.207373132054185</v>
       </c>
       <c r="E5" t="n">
-        <v>15.42221723983943</v>
+        <v>2.506110301473907</v>
       </c>
       <c r="F5" t="n">
-        <v>14.62298148309293</v>
+        <v>2.376234491002601</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.05628996344938</v>
+        <v>3.909147119060524</v>
       </c>
       <c r="D6" t="n">
-        <v>23.74105118730888</v>
+        <v>3.857920817937693</v>
       </c>
       <c r="E6" t="n">
-        <v>15.42221723983943</v>
+        <v>2.506110301473907</v>
       </c>
       <c r="F6" t="n">
-        <v>14.62298148309293</v>
+        <v>2.376234491002601</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.61133190456787</v>
+        <v>2.049341434492278</v>
       </c>
       <c r="D7" t="n">
-        <v>13.13839821983543</v>
+        <v>2.134989710723258</v>
       </c>
       <c r="E7" t="n">
-        <v>15.42221723983943</v>
+        <v>2.506110301473907</v>
       </c>
       <c r="F7" t="n">
-        <v>14.62298148309293</v>
+        <v>2.376234491002601</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.92015943274964</v>
+        <v>7.137025907821816</v>
       </c>
       <c r="D8" t="n">
-        <v>41.48536965335275</v>
+        <v>6.741372568669822</v>
       </c>
       <c r="E8" t="n">
-        <v>15.42221723983943</v>
+        <v>2.506110301473907</v>
       </c>
       <c r="F8" t="n">
-        <v>14.62298148309293</v>
+        <v>2.376234491002601</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
